--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-03-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.25</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.25</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.25</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£10.24</t>
+          <t>£11.78</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -625,57 +625,57 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£12.50</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>£13.53</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>£13.85</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£15.08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£15.98</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£13.07</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>£12.05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>£12.05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£12.50</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£13.53</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£12.04</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£15.08</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£15.98</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£13.07</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£13.05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.87</t>
+          <t>£15.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.87</t>
+          <t>£15.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.87</t>
+          <t>£15.95</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£14.86</t>
+          <t>£17.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£16.05</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.84</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.84</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.84</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£15.83</t>
+          <t>£18.20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£17.83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.65</t>
+          <t>£20.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.65</t>
+          <t>£20.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.65</t>
+          <t>£20.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£19.64</t>
+          <t>£22.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£21.99</t>
+          <t>£25.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£22.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£21.99</t>
+          <t>£25.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.05</t>
+          <t>£26.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.05</t>
+          <t>£26.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.05</t>
+          <t>£26.25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£25.04</t>
+          <t>£28.80</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.40</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.40</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.40</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£27.39</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.67</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.67</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.67</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£26.65</t>
+          <t>£30.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£32.40</t>
+          <t>£36.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£32.40</t>
+          <t>£36.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£32.40</t>
+          <t>£36.25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£32.74</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£39.40</t>
+          <t>£43.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£39.40</t>
+          <t>£43.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£39.40</t>
+          <t>£43.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£39.39</t>
+          <t>£45.30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£39.98</t>
+          <t>£45.98</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>£41.50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>£41.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>£41.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£40.34</t>
+          <t>£46.39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£745.00</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£745.00</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£745.00</t>
+          <t>£765.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£744.00</t>
+          <t>£855.60</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£935.00</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£935.00</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£935.00</t>
+          <t>£985.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£934.00</t>
+          <t>£1,074.10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£28.56</t>
+          <t>£32.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£34.78</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£38.19</t>
+          <t>£43.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£44.55</t>
+          <t>£51.23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£47.47</t>
+          <t>£54.59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£51.26</t>
+          <t>£58.95</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£46.92</t>
+          <t>£53.96</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1198.4</t>
+          <t>£1378.24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>£1333.28</t>
+          <t>£1620.96</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1334.4</t>
+          <t>£1534.56</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>£1533.28</t>
+          <t>£1872.48</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1276.0</t>
+          <t>£1467.36</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>£1517.76</t>
+          <t>£1838.4</t>
         </is>
       </c>
     </row>
